--- a/ProjectConfigTable/exgas_config/Datas/#exgas.ability.xlsx
+++ b/ProjectConfigTable/exgas_config/Datas/#exgas.ability.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\luban_examples-main\luban_examples-main\MiniTemplate\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\MyRepo\gameplay-ability-system-for-unity\ProjectConfigTable\exgas_config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA6FDF8B-7CB8-492B-AB46-CE264B25F843}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D72009E2-8ECA-43F7-9C41-F582112D849F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="32">
   <si>
     <t>##var</t>
   </si>
@@ -39,9 +39,6 @@
     <t>desc</t>
   </si>
   <si>
-    <t>count</t>
-  </si>
-  <si>
     <t>##type</t>
   </si>
   <si>
@@ -60,34 +57,101 @@
     <t>描述</t>
   </si>
   <si>
-    <t>个数</t>
-  </si>
-  <si>
-    <t>道具1</t>
-  </si>
-  <si>
     <t>描述1</t>
   </si>
   <si>
-    <t>道具2</t>
-  </si>
-  <si>
     <t>描述2</t>
   </si>
   <si>
-    <t>asset_tags</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>描述标签</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>16|9</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>(list#sep=|),int</t>
+    <t>assetTags</t>
+  </si>
+  <si>
+    <t>cancelAbilityWithTags</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>blockAbilityWithTags</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>activationOwnedTags</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>activationRequiredTags</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(list#sep=;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>),int</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>activationBlockedTags</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>cost</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>消耗GE</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>cd</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>cdEffect</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>冷却CD时长</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>冷却CD执行的GE</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>abilityLogic</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>AbilityLogic?</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能逻辑：支持多态，添加新AbilityLogic类型去__bean__中添加即可。暂定给了13个变量的预留位，不够的话就自己加长。</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -95,7 +159,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -118,6 +182,25 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF1F2328"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF1F2328"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -127,7 +210,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -135,6 +218,68 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -142,13 +287,36 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFill="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -431,13 +599,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:AA5"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="6" max="6" width="16.77734375" customWidth="1"/>
+    <col min="4" max="6" width="15.33203125" customWidth="1"/>
+    <col min="7" max="7" width="16.109375" customWidth="1"/>
+    <col min="8" max="8" width="16.77734375" customWidth="1"/>
+    <col min="9" max="9" width="20" customWidth="1"/>
+    <col min="10" max="10" width="21.77734375" customWidth="1"/>
+    <col min="11" max="12" width="21" customWidth="1"/>
+    <col min="13" max="13" width="20.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:27" ht="19.8" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -451,92 +625,186 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="L1" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="M1" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="N1" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="O1" s="7"/>
+      <c r="P1" s="7"/>
+      <c r="Q1" s="7"/>
+      <c r="R1" s="7"/>
+      <c r="S1" s="7"/>
+      <c r="T1" s="7"/>
+      <c r="U1" s="7"/>
+      <c r="V1" s="7"/>
+      <c r="W1" s="7"/>
+      <c r="X1" s="7"/>
+      <c r="Y1" s="7"/>
+      <c r="Z1" s="7"/>
+      <c r="AA1" s="8"/>
+    </row>
+    <row r="2" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
-        <v>16</v>
-      </c>
+      <c r="B2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="K2" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="M2" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="N2" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="O2" s="7"/>
+      <c r="P2" s="7"/>
+      <c r="Q2" s="7"/>
+      <c r="R2" s="7"/>
+      <c r="S2" s="7"/>
+      <c r="T2" s="7"/>
+      <c r="U2" s="7"/>
+      <c r="V2" s="7"/>
+      <c r="W2" s="7"/>
+      <c r="X2" s="7"/>
+      <c r="Y2" s="7"/>
+      <c r="Z2" s="7"/>
+      <c r="AA2" s="8"/>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" s="1" t="s">
+    <row r="3" spans="1:27" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
         <v>7</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>8</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>10</v>
-      </c>
       <c r="E3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>17</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N3" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="O3" s="10"/>
+      <c r="P3" s="10"/>
+      <c r="Q3" s="10"/>
+      <c r="R3" s="10"/>
+      <c r="S3" s="10"/>
+      <c r="T3" s="10"/>
+      <c r="U3" s="10"/>
+      <c r="V3" s="10"/>
+      <c r="W3" s="10"/>
+      <c r="X3" s="10"/>
+      <c r="Y3" s="10"/>
+      <c r="Z3" s="10"/>
+      <c r="AA3" s="11"/>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="1">
         <v>10001</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E4" s="1">
         <v>10</v>
       </c>
-      <c r="F4" s="2">
-        <v>115</v>
-      </c>
-      <c r="G4" s="2">
-        <v>15</v>
-      </c>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" s="1">
         <v>10002</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E5" s="1">
-        <v>100</v>
-      </c>
-      <c r="F5" t="s">
-        <v>18</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
     </row>
   </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="N1:AA1"/>
+    <mergeCell ref="N2:AA2"/>
+    <mergeCell ref="N3:AA3"/>
+  </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/ProjectConfigTable/exgas_config/Datas/#exgas.ability.xlsx
+++ b/ProjectConfigTable/exgas_config/Datas/#exgas.ability.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\MyRepo\gameplay-ability-system-for-unity\ProjectConfigTable\exgas_config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D72009E2-8ECA-43F7-9C41-F582112D849F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9253047B-D679-46B9-BECC-B2B3330E84F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -67,9 +67,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>assetTags</t>
-  </si>
-  <si>
     <t>cancelAbilityWithTags</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -152,6 +149,10 @@
   </si>
   <si>
     <t>技能逻辑：支持多态，添加新AbilityLogic类型去__bean__中添加即可。暂定给了13个变量的预留位，不够的话就自己加长。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>assetTags</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -602,8 +603,9 @@
   <dimension ref="A1:AA5"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="4" max="6" width="15.33203125" customWidth="1"/>
-    <col min="7" max="7" width="16.109375" customWidth="1"/>
+    <col min="4" max="5" width="15.33203125" customWidth="1"/>
+    <col min="6" max="6" width="16.109375" customWidth="1"/>
+    <col min="7" max="7" width="15.33203125" customWidth="1"/>
     <col min="8" max="8" width="16.77734375" customWidth="1"/>
     <col min="9" max="9" width="20" customWidth="1"/>
     <col min="10" max="10" width="21.77734375" customWidth="1"/>
@@ -625,34 +627,34 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>25</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="H1" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I1" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="J1" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="K1" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="L1" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="L1" s="4" t="s">
-        <v>17</v>
-      </c>
       <c r="M1" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N1" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O1" s="7"/>
       <c r="P1" s="7"/>
@@ -682,34 +684,34 @@
         <v>6</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L2" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="M2" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N2" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="O2" s="7"/>
       <c r="P2" s="7"/>
@@ -739,19 +741,19 @@
         <v>9</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>27</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>12</v>
       </c>
       <c r="N3" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O3" s="10"/>
       <c r="P3" s="10"/>
@@ -773,7 +775,7 @@
         <v>10001</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>10</v>
@@ -790,7 +792,7 @@
         <v>10002</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>11</v>
@@ -807,5 +809,6 @@
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/ProjectConfigTable/exgas_config/Datas/#exgas.ability.xlsx
+++ b/ProjectConfigTable/exgas_config/Datas/#exgas.ability.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\MyRepo\gameplay-ability-system-for-unity\ProjectConfigTable\exgas_config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9253047B-D679-46B9-BECC-B2B3330E84F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C8639EB-CC6D-429B-A813-D18FE50C2334}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="162913" fullCalcOnLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
   <si>
     <t>##var</t>
   </si>
@@ -39,6 +39,36 @@
     <t>desc</t>
   </si>
   <si>
+    <t>cost</t>
+  </si>
+  <si>
+    <t>cdEffect</t>
+  </si>
+  <si>
+    <t>cd</t>
+  </si>
+  <si>
+    <t>assetTags</t>
+  </si>
+  <si>
+    <t>cancelAbilityWithTags</t>
+  </si>
+  <si>
+    <t>blockAbilityWithTags</t>
+  </si>
+  <si>
+    <t>activationOwnedTags</t>
+  </si>
+  <si>
+    <t>activationRequiredTags</t>
+  </si>
+  <si>
+    <t>activationBlockedTags</t>
+  </si>
+  <si>
+    <t>abilityLogic</t>
+  </si>
+  <si>
     <t>##type</t>
   </si>
   <si>
@@ -48,45 +78,10 @@
     <t>string</t>
   </si>
   <si>
-    <t>##</t>
-  </si>
-  <si>
-    <t>名称</t>
-  </si>
-  <si>
-    <t>描述</t>
-  </si>
-  <si>
-    <t>描述1</t>
-  </si>
-  <si>
-    <t>描述2</t>
-  </si>
-  <si>
-    <t>描述标签</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>cancelAbilityWithTags</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>blockAbilityWithTags</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>activationOwnedTags</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>activationRequiredTags</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
+    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
       <t>(list#sep=;</t>
     </r>
-    <r>
+    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
@@ -97,70 +92,60 @@
       </rPr>
       <t>),int</t>
     </r>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>activationBlockedTags</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>AbilityLogic?</t>
+  </si>
+  <si>
+    <t>##</t>
+  </si>
+  <si>
+    <t>名称</t>
+  </si>
+  <si>
+    <t>描述</t>
+  </si>
+  <si>
+    <t>消耗GE</t>
+  </si>
+  <si>
+    <t>冷却CD执行的GE</t>
+  </si>
+  <si>
+    <t>冷却CD时长</t>
+  </si>
+  <si>
+    <t>描述标签</t>
+  </si>
+  <si>
+    <t>技能逻辑：支持多态，添加新AbilityLogic类型去__bean__中添加即可。暂定给了13个变量的预留位，不够的话就自己加长。</t>
   </si>
   <si>
     <t>技能1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>描述1</t>
   </si>
   <si>
     <t>技能2</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>cost</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>int</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>消耗GE</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>cd</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>cdEffect</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>冷却CD时长</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>冷却CD执行的GE</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>abilityLogic</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>AbilityLogic?</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>技能逻辑：支持多态，添加新AbilityLogic类型去__bean__中添加即可。暂定给了13个变量的预留位，不够的话就自己加长。</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>assetTags</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>描述2</t>
+  </si>
+  <si>
+    <t>100</t>
+  </si>
+  <si>
+    <t/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <numFmts count="0"/>
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -173,14 +158,6 @@
       <color theme="1"/>
       <name val="等线"/>
       <family val="2"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -288,41 +265,42 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1">
+  <cellXfs count="13">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFill="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="3" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="4" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="2" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="2" applyFont="1" fillId="0" applyFill="1" borderId="1" applyBorder="1" xfId="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="2" applyFont="1" fillId="0" applyFill="1" borderId="2" applyBorder="1" xfId="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="2" applyFont="1" fillId="0" applyFill="1" borderId="3" applyBorder="1" xfId="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="2" applyFont="1" fillId="0" applyFill="1" borderId="4" applyBorder="1" xfId="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="2" applyFont="1" fillId="0" applyFill="1" borderId="5" applyBorder="1" xfId="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="2" applyFont="1" fillId="0" applyFill="1" borderId="6" applyBorder="1" xfId="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 2" xfId="1" xr:uid="{55324ADC-B395-4A2E-867E-64A197BD9EA7}"/>
+    <cellStyle name="常规 2" xfId="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -603,17 +581,17 @@
   <dimension ref="A1:AA5"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="4" max="5" width="15.33203125" customWidth="1"/>
-    <col min="6" max="6" width="16.109375" customWidth="1"/>
-    <col min="7" max="7" width="15.33203125" customWidth="1"/>
-    <col min="8" max="8" width="16.77734375" customWidth="1"/>
-    <col min="9" max="9" width="20" customWidth="1"/>
-    <col min="10" max="10" width="21.77734375" customWidth="1"/>
-    <col min="11" max="12" width="21" customWidth="1"/>
-    <col min="13" max="13" width="20.21875" customWidth="1"/>
+    <col min="4" max="5" width="15.33203125" customWidth="1" style="2"/>
+    <col min="6" max="6" width="16.109375" customWidth="1" style="2"/>
+    <col min="7" max="7" width="15.33203125" customWidth="1" style="2"/>
+    <col min="8" max="8" width="16.77734375" customWidth="1" style="2"/>
+    <col min="9" max="9" width="20" customWidth="1" style="2"/>
+    <col min="10" max="10" width="21.77734375" customWidth="1" style="2"/>
+    <col min="11" max="12" width="21" customWidth="1" style="2"/>
+    <col min="13" max="13" width="20.21875" customWidth="1" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="19.8" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="1" ht="19.8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -627,188 +605,213 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I1" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="O1" s="8"/>
+      <c r="P1" s="8"/>
+      <c r="Q1" s="8"/>
+      <c r="R1" s="8"/>
+      <c r="S1" s="8"/>
+      <c r="T1" s="8"/>
+      <c r="U1" s="8"/>
+      <c r="V1" s="8"/>
+      <c r="W1" s="8"/>
+      <c r="X1" s="8"/>
+      <c r="Y1" s="8"/>
+      <c r="Z1" s="8"/>
+      <c r="AA1" s="9"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="B2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="C2" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="D2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H2" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="J2" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="K2" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="L2" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="M2" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="N2" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="N1" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="O1" s="7"/>
-      <c r="P1" s="7"/>
-      <c r="Q1" s="7"/>
-      <c r="R1" s="7"/>
-      <c r="S1" s="7"/>
-      <c r="T1" s="7"/>
-      <c r="U1" s="7"/>
-      <c r="V1" s="7"/>
-      <c r="W1" s="7"/>
-      <c r="X1" s="7"/>
-      <c r="Y1" s="7"/>
-      <c r="Z1" s="7"/>
-      <c r="AA1" s="8"/>
+      <c r="O2" s="8"/>
+      <c r="P2" s="8"/>
+      <c r="Q2" s="8"/>
+      <c r="R2" s="8"/>
+      <c r="S2" s="8"/>
+      <c r="T2" s="8"/>
+      <c r="U2" s="8"/>
+      <c r="V2" s="8"/>
+      <c r="W2" s="8"/>
+      <c r="X2" s="8"/>
+      <c r="Y2" s="8"/>
+      <c r="Z2" s="8"/>
+      <c r="AA2" s="9"/>
     </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="H2" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="I2" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J2" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="K2" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="L2" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="M2" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="N2" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="O2" s="7"/>
-      <c r="P2" s="7"/>
-      <c r="Q2" s="7"/>
-      <c r="R2" s="7"/>
-      <c r="S2" s="7"/>
-      <c r="T2" s="7"/>
-      <c r="U2" s="7"/>
-      <c r="V2" s="7"/>
-      <c r="W2" s="7"/>
-      <c r="X2" s="7"/>
-      <c r="Y2" s="7"/>
-      <c r="Z2" s="7"/>
-      <c r="AA2" s="8"/>
-    </row>
-    <row r="3" spans="1:27" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" ht="14.4">
       <c r="A3" s="1" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="E3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F3" s="1" t="s">
-        <v>27</v>
-      </c>
       <c r="G3" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="N3" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="H3" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="N3" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="O3" s="10"/>
-      <c r="P3" s="10"/>
-      <c r="Q3" s="10"/>
-      <c r="R3" s="10"/>
-      <c r="S3" s="10"/>
-      <c r="T3" s="10"/>
-      <c r="U3" s="10"/>
-      <c r="V3" s="10"/>
-      <c r="W3" s="10"/>
-      <c r="X3" s="10"/>
-      <c r="Y3" s="10"/>
-      <c r="Z3" s="10"/>
-      <c r="AA3" s="11"/>
+      <c r="O3" s="11"/>
+      <c r="P3" s="11"/>
+      <c r="Q3" s="11"/>
+      <c r="R3" s="11"/>
+      <c r="S3" s="11"/>
+      <c r="T3" s="11"/>
+      <c r="U3" s="11"/>
+      <c r="V3" s="11"/>
+      <c r="W3" s="11"/>
+      <c r="X3" s="11"/>
+      <c r="Y3" s="11"/>
+      <c r="Z3" s="11"/>
+      <c r="AA3" s="12"/>
     </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="4">
       <c r="A4" s="1"/>
       <c r="B4" s="1">
         <v>10001</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
     </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="5">
       <c r="A5" s="1"/>
       <c r="B5" s="1">
         <v>10002</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
+        <v>30</v>
+      </c>
+      <c r="E5" s="1">
+        <v>-3</v>
+      </c>
+      <c r="F5" s="1">
+        <v>-14</v>
+      </c>
+      <c r="G5" s="1">
+        <v>-14</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="M5" s="2" t="s">
+        <v>32</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells>
     <mergeCell ref="N1:AA1"/>
     <mergeCell ref="N2:AA2"/>
     <mergeCell ref="N3:AA3"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/ProjectConfigTable/exgas_config/Datas/#exgas.ability.xlsx
+++ b/ProjectConfigTable/exgas_config/Datas/#exgas.ability.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\MyRepo\gameplay-ability-system-for-unity\ProjectConfigTable\exgas_config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C8639EB-CC6D-429B-A813-D18FE50C2334}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE34EA30-42A8-4D46-B526-309217077771}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
   <si>
     <t>##var</t>
   </si>
@@ -128,6 +128,21 @@
     <t>描述1</t>
   </si>
   <si>
+    <t>1001;2001;2003;2002</t>
+  </si>
+  <si>
+    <t>2002;2005;2004</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>ALDebugLog</t>
+  </si>
+  <si>
+    <t>测试代码1</t>
+  </si>
+  <si>
     <t>技能2</t>
   </si>
   <si>
@@ -137,7 +152,7 @@
     <t>100</t>
   </si>
   <si>
-    <t/>
+    <t>测试代码2</t>
   </si>
 </sst>
 </file>
@@ -265,11 +280,13 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
     <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
     <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
     <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
       <alignment vertical="center"/>
@@ -581,17 +598,18 @@
   <dimension ref="A1:AA5"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="4" max="5" width="15.33203125" customWidth="1" style="2"/>
-    <col min="6" max="6" width="16.109375" customWidth="1" style="2"/>
-    <col min="7" max="7" width="15.33203125" customWidth="1" style="2"/>
-    <col min="8" max="8" width="16.77734375" customWidth="1" style="2"/>
-    <col min="9" max="9" width="20" customWidth="1" style="2"/>
-    <col min="10" max="10" width="21.77734375" customWidth="1" style="2"/>
-    <col min="11" max="12" width="21" customWidth="1" style="2"/>
-    <col min="13" max="13" width="20.21875" customWidth="1" style="2"/>
+    <col min="4" max="5" width="15.33203125" customWidth="1" style="4"/>
+    <col min="6" max="6" width="16.109375" customWidth="1" style="4"/>
+    <col min="7" max="7" width="15.33203125" customWidth="1" style="4"/>
+    <col min="8" max="8" width="16.77734375" customWidth="1" style="4"/>
+    <col min="9" max="9" width="20" customWidth="1" style="4"/>
+    <col min="10" max="10" width="21.77734375" customWidth="1" style="4"/>
+    <col min="11" max="12" width="21" customWidth="1" style="4"/>
+    <col min="13" max="13" width="20.21875" customWidth="1" style="4"/>
+    <col min="14" max="14" width="16.109375" customWidth="1" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" ht="19.8">
+    <row r="1" ht="19.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -613,40 +631,40 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="J1" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="K1" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="L1" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="5" t="s">
+      <c r="M1" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="7" t="s">
+      <c r="N1" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="8"/>
-      <c r="P1" s="8"/>
-      <c r="Q1" s="8"/>
-      <c r="R1" s="8"/>
-      <c r="S1" s="8"/>
-      <c r="T1" s="8"/>
-      <c r="U1" s="8"/>
-      <c r="V1" s="8"/>
-      <c r="W1" s="8"/>
-      <c r="X1" s="8"/>
-      <c r="Y1" s="8"/>
-      <c r="Z1" s="8"/>
-      <c r="AA1" s="9"/>
+      <c r="O1" s="10"/>
+      <c r="P1" s="10"/>
+      <c r="Q1" s="10"/>
+      <c r="R1" s="10"/>
+      <c r="S1" s="10"/>
+      <c r="T1" s="10"/>
+      <c r="U1" s="10"/>
+      <c r="V1" s="10"/>
+      <c r="W1" s="10"/>
+      <c r="X1" s="10"/>
+      <c r="Y1" s="10"/>
+      <c r="Z1" s="10"/>
+      <c r="AA1" s="11"/>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
@@ -670,42 +688,42 @@
       <c r="G2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="H2" s="6" t="s">
+      <c r="H2" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="I2" s="6" t="s">
+      <c r="I2" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="J2" s="6" t="s">
+      <c r="J2" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="K2" s="6" t="s">
+      <c r="K2" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="L2" s="6" t="s">
+      <c r="L2" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="M2" s="6" t="s">
+      <c r="M2" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N2" s="7" t="s">
+      <c r="N2" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="O2" s="8"/>
-      <c r="P2" s="8"/>
-      <c r="Q2" s="8"/>
-      <c r="R2" s="8"/>
-      <c r="S2" s="8"/>
-      <c r="T2" s="8"/>
-      <c r="U2" s="8"/>
-      <c r="V2" s="8"/>
-      <c r="W2" s="8"/>
-      <c r="X2" s="8"/>
-      <c r="Y2" s="8"/>
-      <c r="Z2" s="8"/>
-      <c r="AA2" s="9"/>
+      <c r="O2" s="10"/>
+      <c r="P2" s="10"/>
+      <c r="Q2" s="10"/>
+      <c r="R2" s="10"/>
+      <c r="S2" s="10"/>
+      <c r="T2" s="10"/>
+      <c r="U2" s="10"/>
+      <c r="V2" s="10"/>
+      <c r="W2" s="10"/>
+      <c r="X2" s="10"/>
+      <c r="Y2" s="10"/>
+      <c r="Z2" s="10"/>
+      <c r="AA2" s="11"/>
     </row>
-    <row r="3" ht="14.4">
+    <row r="3">
       <c r="A3" s="1" t="s">
         <v>19</v>
       </c>
@@ -727,25 +745,25 @@
       <c r="G3" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="H3" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="N3" s="10" t="s">
+      <c r="N3" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="O3" s="11"/>
-      <c r="P3" s="11"/>
-      <c r="Q3" s="11"/>
-      <c r="R3" s="11"/>
-      <c r="S3" s="11"/>
-      <c r="T3" s="11"/>
-      <c r="U3" s="11"/>
-      <c r="V3" s="11"/>
-      <c r="W3" s="11"/>
-      <c r="X3" s="11"/>
-      <c r="Y3" s="11"/>
-      <c r="Z3" s="11"/>
-      <c r="AA3" s="12"/>
+      <c r="O3" s="13"/>
+      <c r="P3" s="13"/>
+      <c r="Q3" s="13"/>
+      <c r="R3" s="13"/>
+      <c r="S3" s="13"/>
+      <c r="T3" s="13"/>
+      <c r="U3" s="13"/>
+      <c r="V3" s="13"/>
+      <c r="W3" s="13"/>
+      <c r="X3" s="13"/>
+      <c r="Y3" s="13"/>
+      <c r="Z3" s="13"/>
+      <c r="AA3" s="14"/>
     </row>
     <row r="4">
       <c r="A4" s="1"/>
@@ -758,11 +776,39 @@
       <c r="D4" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
+      <c r="E4" s="1">
+        <v>1001</v>
+      </c>
+      <c r="F4" s="1">
+        <v>1001</v>
+      </c>
+      <c r="G4" s="1">
+        <v>96</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="K4" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="L4" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="M4" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="N4" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="O4" s="3" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1"/>
@@ -770,10 +816,10 @@
         <v>10002</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="E5" s="1">
         <v>-3</v>
@@ -784,23 +830,29 @@
       <c r="G5" s="1">
         <v>-14</v>
       </c>
-      <c r="H5" s="2" t="s">
+      <c r="H5" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="I5" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="I5" s="2" t="s">
+      <c r="J5" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="K5" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="L5" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="M5" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="N5" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="J5" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="L5" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="M5" s="2" t="s">
-        <v>32</v>
+      <c r="O5" s="4" t="s">
+        <v>37</v>
       </c>
     </row>
   </sheetData>

--- a/ProjectConfigTable/exgas_config/Datas/#exgas.ability.xlsx
+++ b/ProjectConfigTable/exgas_config/Datas/#exgas.ability.xlsx
@@ -140,7 +140,7 @@
     <t>ALDebugLog</t>
   </si>
   <si>
-    <t>测试代码1</t>
+    <t>测试代码9</t>
   </si>
   <si>
     <t>技能2</t>

--- a/ProjectConfigTable/exgas_config/Datas/#exgas.ability.xlsx
+++ b/ProjectConfigTable/exgas_config/Datas/#exgas.ability.xlsx
@@ -8,24 +8,27 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\MyRepo\gameplay-ability-system-for-unity\ProjectConfigTable\exgas_config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE34EA30-42A8-4D46-B526-309217077771}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10DCD1AD-B3A4-47D8-A920-0F285C7DE4B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913" fullCalcOnLoad="1"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="37">
   <si>
     <t>##var</t>
   </si>
@@ -78,10 +81,10 @@
     <t>string</t>
   </si>
   <si>
-    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+    <r>
       <t>(list#sep=;</t>
     </r>
-    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+    <r>
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
@@ -92,7 +95,7 @@
       </rPr>
       <t>),int</t>
     </r>
-    <phoneticPr xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" fontId="4" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>AbilityLogic?</t>
@@ -147,9 +150,6 @@
   </si>
   <si>
     <t>描述2</t>
-  </si>
-  <si>
-    <t>100</t>
   </si>
   <si>
     <t>测试代码2</t>
@@ -159,8 +159,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -194,6 +193,14 @@
       <name val="Segoe UI"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -280,44 +287,43 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
+  <cellXfs count="14">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="3" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="4" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="2" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="2" applyFont="1" fillId="0" applyFill="1" borderId="1" applyBorder="1" xfId="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="2" applyFont="1" fillId="0" applyFill="1" borderId="2" applyBorder="1" xfId="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="2" applyFont="1" fillId="0" applyFill="1" borderId="3" applyBorder="1" xfId="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="2" applyFont="1" fillId="0" applyFill="1" borderId="4" applyBorder="1" xfId="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="2" applyFont="1" fillId="0" applyFill="1" borderId="5" applyBorder="1" xfId="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="2" applyFont="1" fillId="0" applyFill="1" borderId="6" applyBorder="1" xfId="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 2" xfId="1"/>
+    <cellStyle name="常规 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -598,18 +604,18 @@
   <dimension ref="A1:AA5"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="4" max="5" width="15.33203125" customWidth="1" style="4"/>
-    <col min="6" max="6" width="16.109375" customWidth="1" style="4"/>
-    <col min="7" max="7" width="15.33203125" customWidth="1" style="4"/>
-    <col min="8" max="8" width="16.77734375" customWidth="1" style="4"/>
-    <col min="9" max="9" width="20" customWidth="1" style="4"/>
-    <col min="10" max="10" width="21.77734375" customWidth="1" style="4"/>
-    <col min="11" max="12" width="21" customWidth="1" style="4"/>
-    <col min="13" max="13" width="20.21875" customWidth="1" style="4"/>
-    <col min="14" max="14" width="16.109375" customWidth="1" style="3"/>
+    <col min="4" max="5" width="15.33203125" style="3" customWidth="1"/>
+    <col min="6" max="6" width="16.109375" style="3" customWidth="1"/>
+    <col min="7" max="7" width="15.33203125" style="3" customWidth="1"/>
+    <col min="8" max="8" width="16.77734375" style="3" customWidth="1"/>
+    <col min="9" max="9" width="20" style="3" customWidth="1"/>
+    <col min="10" max="10" width="21.77734375" style="3" customWidth="1"/>
+    <col min="11" max="12" width="21" style="3" customWidth="1"/>
+    <col min="13" max="13" width="20.21875" style="3" customWidth="1"/>
+    <col min="14" max="14" width="16.109375" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="19.2">
+    <row r="1" spans="1:27" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -631,42 +637,42 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="H1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="I1" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="7" t="s">
+      <c r="J1" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="7" t="s">
+      <c r="K1" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="7" t="s">
+      <c r="L1" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="7" t="s">
+      <c r="M1" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="9" t="s">
+      <c r="N1" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="10"/>
-      <c r="P1" s="10"/>
-      <c r="Q1" s="10"/>
-      <c r="R1" s="10"/>
-      <c r="S1" s="10"/>
-      <c r="T1" s="10"/>
-      <c r="U1" s="10"/>
-      <c r="V1" s="10"/>
-      <c r="W1" s="10"/>
-      <c r="X1" s="10"/>
-      <c r="Y1" s="10"/>
-      <c r="Z1" s="10"/>
-      <c r="AA1" s="11"/>
+      <c r="O1" s="9"/>
+      <c r="P1" s="9"/>
+      <c r="Q1" s="9"/>
+      <c r="R1" s="9"/>
+      <c r="S1" s="9"/>
+      <c r="T1" s="9"/>
+      <c r="U1" s="9"/>
+      <c r="V1" s="9"/>
+      <c r="W1" s="9"/>
+      <c r="X1" s="9"/>
+      <c r="Y1" s="9"/>
+      <c r="Z1" s="9"/>
+      <c r="AA1" s="10"/>
     </row>
-    <row r="2">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>14</v>
       </c>
@@ -688,42 +694,42 @@
       <c r="G2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="H2" s="8" t="s">
+      <c r="H2" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="I2" s="8" t="s">
+      <c r="I2" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="J2" s="8" t="s">
+      <c r="J2" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="K2" s="8" t="s">
+      <c r="K2" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="L2" s="8" t="s">
+      <c r="L2" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="M2" s="8" t="s">
+      <c r="M2" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="N2" s="9" t="s">
+      <c r="N2" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="O2" s="10"/>
-      <c r="P2" s="10"/>
-      <c r="Q2" s="10"/>
-      <c r="R2" s="10"/>
-      <c r="S2" s="10"/>
-      <c r="T2" s="10"/>
-      <c r="U2" s="10"/>
-      <c r="V2" s="10"/>
-      <c r="W2" s="10"/>
-      <c r="X2" s="10"/>
-      <c r="Y2" s="10"/>
-      <c r="Z2" s="10"/>
-      <c r="AA2" s="11"/>
+      <c r="O2" s="9"/>
+      <c r="P2" s="9"/>
+      <c r="Q2" s="9"/>
+      <c r="R2" s="9"/>
+      <c r="S2" s="9"/>
+      <c r="T2" s="9"/>
+      <c r="U2" s="9"/>
+      <c r="V2" s="9"/>
+      <c r="W2" s="9"/>
+      <c r="X2" s="9"/>
+      <c r="Y2" s="9"/>
+      <c r="Z2" s="9"/>
+      <c r="AA2" s="10"/>
     </row>
-    <row r="3">
+    <row r="3" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>19</v>
       </c>
@@ -745,27 +751,27 @@
       <c r="G3" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="H3" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="N3" s="12" t="s">
+      <c r="N3" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="O3" s="13"/>
-      <c r="P3" s="13"/>
-      <c r="Q3" s="13"/>
-      <c r="R3" s="13"/>
-      <c r="S3" s="13"/>
-      <c r="T3" s="13"/>
-      <c r="U3" s="13"/>
-      <c r="V3" s="13"/>
-      <c r="W3" s="13"/>
-      <c r="X3" s="13"/>
-      <c r="Y3" s="13"/>
-      <c r="Z3" s="13"/>
-      <c r="AA3" s="14"/>
+      <c r="O3" s="12"/>
+      <c r="P3" s="12"/>
+      <c r="Q3" s="12"/>
+      <c r="R3" s="12"/>
+      <c r="S3" s="12"/>
+      <c r="T3" s="12"/>
+      <c r="U3" s="12"/>
+      <c r="V3" s="12"/>
+      <c r="W3" s="12"/>
+      <c r="X3" s="12"/>
+      <c r="Y3" s="12"/>
+      <c r="Z3" s="12"/>
+      <c r="AA3" s="13"/>
     </row>
-    <row r="4">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="1">
         <v>10001</v>
@@ -785,32 +791,32 @@
       <c r="G4" s="1">
         <v>96</v>
       </c>
-      <c r="H4" s="5" t="s">
+      <c r="H4" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="I4" s="5" t="s">
+      <c r="I4" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="J4" s="4" t="s">
+      <c r="J4" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="K4" s="4" t="s">
+      <c r="K4" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="L4" s="4" t="s">
+      <c r="L4" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="M4" s="4" t="s">
+      <c r="M4" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="N4" s="4" t="s">
+      <c r="N4" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="O4" s="3" t="s">
+      <c r="O4" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" s="1">
         <v>10002</v>
@@ -821,42 +827,42 @@
       <c r="D5" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="E5" s="1">
-        <v>-3</v>
-      </c>
-      <c r="F5" s="1">
-        <v>-14</v>
+      <c r="E5" s="4">
+        <v>1001</v>
+      </c>
+      <c r="F5" s="4">
+        <v>1001</v>
       </c>
       <c r="G5" s="1">
-        <v>-14</v>
-      </c>
-      <c r="H5" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="H5" s="3">
+        <v>1001</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="M5" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N5" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="O5" s="3" t="s">
         <v>36</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="J5" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="K5" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="L5" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="M5" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="N5" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="O5" s="4" t="s">
-        <v>37</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells>
+  <mergeCells count="3">
     <mergeCell ref="N1:AA1"/>
     <mergeCell ref="N2:AA2"/>
     <mergeCell ref="N3:AA3"/>
@@ -864,6 +870,5 @@
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/ProjectConfigTable/exgas_config/Datas/#exgas.ability.xlsx
+++ b/ProjectConfigTable/exgas_config/Datas/#exgas.ability.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\MyRepo\gameplay-ability-system-for-unity\ProjectConfigTable\exgas_config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10DCD1AD-B3A4-47D8-A920-0F285C7DE4B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56766591-6671-4143-AD53-B2EC711AD171}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -125,9 +125,6 @@
     <t>技能逻辑：支持多态，添加新AbilityLogic类型去__bean__中添加即可。暂定给了13个变量的预留位，不够的话就自己加长。</t>
   </si>
   <si>
-    <t>技能1</t>
-  </si>
-  <si>
     <t>描述1</t>
   </si>
   <si>
@@ -146,13 +143,16 @@
     <t>测试代码9</t>
   </si>
   <si>
-    <t>技能2</t>
-  </si>
-  <si>
     <t>描述2</t>
   </si>
   <si>
     <t>测试代码2</t>
+  </si>
+  <si>
+    <t>move</t>
+  </si>
+  <si>
+    <t>RunSpeedUp</t>
   </si>
 </sst>
 </file>
@@ -729,7 +729,7 @@
       <c r="Z2" s="9"/>
       <c r="AA2" s="10"/>
     </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:27" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>19</v>
       </c>
@@ -776,11 +776,11 @@
       <c r="B4" s="1">
         <v>10001</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>27</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>28</v>
       </c>
       <c r="E4" s="1">
         <v>1001</v>
@@ -792,28 +792,28 @@
         <v>96</v>
       </c>
       <c r="H4" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="I4" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="I4" s="4" t="s">
+      <c r="J4" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="J4" s="3" t="s">
+      <c r="K4" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N4" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="K4" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="L4" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="M4" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="N4" s="3" t="s">
+      <c r="O4" s="2" t="s">
         <v>32</v>
-      </c>
-      <c r="O4" s="2" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:27" x14ac:dyDescent="0.25">
@@ -821,11 +821,11 @@
       <c r="B5" s="1">
         <v>10002</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>34</v>
+      <c r="C5" s="4" t="s">
+        <v>36</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E5" s="4">
         <v>1001</v>
@@ -840,25 +840,25 @@
         <v>1001</v>
       </c>
       <c r="I5" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="M5" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N5" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="J5" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="K5" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="L5" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="M5" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="N5" s="3" t="s">
-        <v>32</v>
-      </c>
       <c r="O5" s="3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>

--- a/ProjectConfigTable/exgas_config/Datas/#exgas.ability.xlsx
+++ b/ProjectConfigTable/exgas_config/Datas/#exgas.ability.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\MyRepo\gameplay-ability-system-for-unity\ProjectConfigTable\exgas_config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56766591-6671-4143-AD53-B2EC711AD171}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9830FEAC-B074-4DE8-BCF4-1E615F359828}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="35">
   <si>
     <t>##var</t>
   </si>
@@ -125,34 +125,28 @@
     <t>技能逻辑：支持多态，添加新AbilityLogic类型去__bean__中添加即可。暂定给了13个变量的预留位，不够的话就自己加长。</t>
   </si>
   <si>
-    <t>描述1</t>
-  </si>
-  <si>
-    <t>1001;2001;2003;2002</t>
-  </si>
-  <si>
-    <t>2002;2005;2004</t>
+    <t>move</t>
+  </si>
+  <si>
+    <t>移动</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
+    <t>ALMove</t>
+  </si>
+  <si>
+    <t>RunSpeedUp</t>
+  </si>
+  <si>
+    <t>描述2</t>
+  </si>
+  <si>
     <t>ALDebugLog</t>
   </si>
   <si>
-    <t>测试代码9</t>
-  </si>
-  <si>
-    <t>描述2</t>
-  </si>
-  <si>
     <t>测试代码2</t>
-  </si>
-  <si>
-    <t>move</t>
-  </si>
-  <si>
-    <t>RunSpeedUp</t>
   </si>
 </sst>
 </file>
@@ -607,7 +601,7 @@
     <col min="4" max="5" width="15.33203125" style="3" customWidth="1"/>
     <col min="6" max="6" width="16.109375" style="3" customWidth="1"/>
     <col min="7" max="7" width="15.33203125" style="3" customWidth="1"/>
-    <col min="8" max="8" width="16.77734375" style="3" customWidth="1"/>
+    <col min="8" max="8" width="23.6640625" style="3" customWidth="1"/>
     <col min="9" max="9" width="20" style="3" customWidth="1"/>
     <col min="10" max="10" width="21.77734375" style="3" customWidth="1"/>
     <col min="11" max="12" width="21" style="3" customWidth="1"/>
@@ -729,7 +723,7 @@
       <c r="Z2" s="9"/>
       <c r="AA2" s="10"/>
     </row>
-    <row r="3" spans="1:27" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>19</v>
       </c>
@@ -777,43 +771,43 @@
         <v>10001</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E4" s="1">
-        <v>1001</v>
-      </c>
-      <c r="F4" s="1">
-        <v>1001</v>
-      </c>
-      <c r="G4" s="1">
-        <v>96</v>
-      </c>
-      <c r="H4" s="4" t="s">
         <v>28</v>
       </c>
+      <c r="E4" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H4" s="4">
+        <v>2002</v>
+      </c>
       <c r="I4" s="4" t="s">
         <v>29</v>
       </c>
       <c r="J4" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="N4" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="K4" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="L4" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="M4" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="N4" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="O4" s="2" t="s">
-        <v>32</v>
+      <c r="O4" s="2">
+        <v>0.5</v>
       </c>
     </row>
     <row r="5" spans="1:27" x14ac:dyDescent="0.25">
@@ -822,10 +816,10 @@
         <v>10002</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E5" s="4">
         <v>1001</v>
@@ -840,22 +834,22 @@
         <v>1001</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="O5" s="3" t="s">
         <v>34</v>

--- a/ProjectConfigTable/exgas_config/Datas/#exgas.ability.xlsx
+++ b/ProjectConfigTable/exgas_config/Datas/#exgas.ability.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\MyRepo\gameplay-ability-system-for-unity\ProjectConfigTable\exgas_config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9830FEAC-B074-4DE8-BCF4-1E615F359828}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD78F964-1011-42B3-8A57-266E772E42CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="34">
   <si>
     <t>##var</t>
   </si>
@@ -140,13 +140,11 @@
     <t>RunSpeedUp</t>
   </si>
   <si>
-    <t>描述2</t>
-  </si>
-  <si>
-    <t>ALDebugLog</t>
-  </si>
-  <si>
-    <t>测试代码2</t>
+    <t>加速</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ALApplyEffect</t>
   </si>
 </sst>
 </file>
@@ -821,18 +819,9 @@
       <c r="D5" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E5" s="4">
-        <v>1001</v>
-      </c>
-      <c r="F5" s="4">
-        <v>1001</v>
-      </c>
-      <c r="G5" s="1">
-        <v>5</v>
-      </c>
-      <c r="H5" s="3">
-        <v>1001</v>
-      </c>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+      <c r="G5" s="1"/>
       <c r="I5" s="3" t="s">
         <v>29</v>
       </c>
@@ -851,8 +840,8 @@
       <c r="N5" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="O5" s="3" t="s">
-        <v>34</v>
+      <c r="O5" s="3">
+        <v>1001</v>
       </c>
     </row>
   </sheetData>

--- a/ProjectConfigTable/exgas_config/Datas/#exgas.ability.xlsx
+++ b/ProjectConfigTable/exgas_config/Datas/#exgas.ability.xlsx
@@ -15,7 +15,7 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="162913" fullCalcOnLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
   <si>
     <t>##var</t>
   </si>
@@ -81,10 +81,10 @@
     <t>string</t>
   </si>
   <si>
-    <r>
+    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
       <t>(list#sep=;</t>
     </r>
-    <r>
+    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
@@ -95,7 +95,7 @@
       </rPr>
       <t>),int</t>
     </r>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>AbilityLogic?</t>
@@ -141,17 +141,20 @@
   </si>
   <si>
     <t>加速</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>ALApplyEffect</t>
+  </si>
+  <si>
+    <t>1002</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <numFmts count="0"/>
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -185,14 +188,6 @@
       <name val="Segoe UI"/>
       <family val="2"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <family val="2"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -279,43 +274,44 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+  <cellXfs count="15">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="3" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="4" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="2" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="2" applyFont="1" fillId="0" applyFill="1" borderId="1" applyBorder="1" xfId="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="2" applyFont="1" fillId="0" applyFill="1" borderId="2" applyBorder="1" xfId="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="2" applyFont="1" fillId="0" applyFill="1" borderId="3" applyBorder="1" xfId="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="2" applyFont="1" fillId="0" applyFill="1" borderId="4" applyBorder="1" xfId="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="2" applyFont="1" fillId="0" applyFill="1" borderId="5" applyBorder="1" xfId="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="2" applyFont="1" fillId="0" applyFill="1" borderId="6" applyBorder="1" xfId="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="常规 2" xfId="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -596,18 +592,18 @@
   <dimension ref="A1:AA5"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="4" max="5" width="15.33203125" style="3" customWidth="1"/>
-    <col min="6" max="6" width="16.109375" style="3" customWidth="1"/>
-    <col min="7" max="7" width="15.33203125" style="3" customWidth="1"/>
-    <col min="8" max="8" width="23.6640625" style="3" customWidth="1"/>
-    <col min="9" max="9" width="20" style="3" customWidth="1"/>
-    <col min="10" max="10" width="21.77734375" style="3" customWidth="1"/>
-    <col min="11" max="12" width="21" style="3" customWidth="1"/>
-    <col min="13" max="13" width="20.21875" style="3" customWidth="1"/>
-    <col min="14" max="14" width="16.109375" style="2" customWidth="1"/>
+    <col min="4" max="5" width="15.33203125" customWidth="1" style="4"/>
+    <col min="6" max="6" width="16.109375" customWidth="1" style="4"/>
+    <col min="7" max="7" width="15.33203125" customWidth="1" style="4"/>
+    <col min="8" max="8" width="23.6640625" customWidth="1" style="4"/>
+    <col min="9" max="9" width="20" customWidth="1" style="4"/>
+    <col min="10" max="10" width="21.77734375" customWidth="1" style="4"/>
+    <col min="11" max="12" width="21" customWidth="1" style="4"/>
+    <col min="13" max="13" width="20.21875" customWidth="1" style="4"/>
+    <col min="14" max="14" width="16.109375" customWidth="1" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="19.2" x14ac:dyDescent="0.45">
+    <row r="1" ht="19.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -629,42 +625,42 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="I1" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="J1" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="K1" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="6" t="s">
+      <c r="L1" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="6" t="s">
+      <c r="M1" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="8" t="s">
+      <c r="N1" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="9"/>
-      <c r="P1" s="9"/>
-      <c r="Q1" s="9"/>
-      <c r="R1" s="9"/>
-      <c r="S1" s="9"/>
-      <c r="T1" s="9"/>
-      <c r="U1" s="9"/>
-      <c r="V1" s="9"/>
-      <c r="W1" s="9"/>
-      <c r="X1" s="9"/>
-      <c r="Y1" s="9"/>
-      <c r="Z1" s="9"/>
-      <c r="AA1" s="10"/>
+      <c r="O1" s="10"/>
+      <c r="P1" s="10"/>
+      <c r="Q1" s="10"/>
+      <c r="R1" s="10"/>
+      <c r="S1" s="10"/>
+      <c r="T1" s="10"/>
+      <c r="U1" s="10"/>
+      <c r="V1" s="10"/>
+      <c r="W1" s="10"/>
+      <c r="X1" s="10"/>
+      <c r="Y1" s="10"/>
+      <c r="Z1" s="10"/>
+      <c r="AA1" s="11"/>
     </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="2">
       <c r="A2" s="1" t="s">
         <v>14</v>
       </c>
@@ -686,42 +682,42 @@
       <c r="G2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="H2" s="7" t="s">
+      <c r="H2" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="I2" s="7" t="s">
+      <c r="I2" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="J2" s="7" t="s">
+      <c r="J2" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="K2" s="7" t="s">
+      <c r="K2" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="L2" s="7" t="s">
+      <c r="L2" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="M2" s="7" t="s">
+      <c r="M2" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N2" s="8" t="s">
+      <c r="N2" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="O2" s="9"/>
-      <c r="P2" s="9"/>
-      <c r="Q2" s="9"/>
-      <c r="R2" s="9"/>
-      <c r="S2" s="9"/>
-      <c r="T2" s="9"/>
-      <c r="U2" s="9"/>
-      <c r="V2" s="9"/>
-      <c r="W2" s="9"/>
-      <c r="X2" s="9"/>
-      <c r="Y2" s="9"/>
-      <c r="Z2" s="9"/>
-      <c r="AA2" s="10"/>
+      <c r="O2" s="10"/>
+      <c r="P2" s="10"/>
+      <c r="Q2" s="10"/>
+      <c r="R2" s="10"/>
+      <c r="S2" s="10"/>
+      <c r="T2" s="10"/>
+      <c r="U2" s="10"/>
+      <c r="V2" s="10"/>
+      <c r="W2" s="10"/>
+      <c r="X2" s="10"/>
+      <c r="Y2" s="10"/>
+      <c r="Z2" s="10"/>
+      <c r="AA2" s="11"/>
     </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="3">
       <c r="A3" s="1" t="s">
         <v>19</v>
       </c>
@@ -743,32 +739,32 @@
       <c r="G3" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="H3" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="N3" s="11" t="s">
+      <c r="N3" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="O3" s="12"/>
-      <c r="P3" s="12"/>
-      <c r="Q3" s="12"/>
-      <c r="R3" s="12"/>
-      <c r="S3" s="12"/>
-      <c r="T3" s="12"/>
-      <c r="U3" s="12"/>
-      <c r="V3" s="12"/>
-      <c r="W3" s="12"/>
-      <c r="X3" s="12"/>
-      <c r="Y3" s="12"/>
-      <c r="Z3" s="12"/>
-      <c r="AA3" s="13"/>
+      <c r="O3" s="13"/>
+      <c r="P3" s="13"/>
+      <c r="Q3" s="13"/>
+      <c r="R3" s="13"/>
+      <c r="S3" s="13"/>
+      <c r="T3" s="13"/>
+      <c r="U3" s="13"/>
+      <c r="V3" s="13"/>
+      <c r="W3" s="13"/>
+      <c r="X3" s="13"/>
+      <c r="Y3" s="13"/>
+      <c r="Z3" s="13"/>
+      <c r="AA3" s="14"/>
     </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="4">
       <c r="A4" s="1"/>
       <c r="B4" s="1">
         <v>10001</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="5" t="s">
         <v>27</v>
       </c>
       <c r="D4" s="1" t="s">
@@ -783,69 +779,78 @@
       <c r="G4" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="H4" s="4">
+      <c r="H4" s="5">
         <v>2002</v>
       </c>
-      <c r="I4" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="K4" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="L4" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="M4" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="N4" s="3" t="s">
+      <c r="I4" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="K4" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="L4" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="M4" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="N4" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="O4" s="2">
+      <c r="O4" s="3">
         <v>0.5</v>
       </c>
     </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="5">
       <c r="A5" s="1"/>
       <c r="B5" s="1">
         <v>10002</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="5" t="s">
         <v>31</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
-      <c r="G5" s="1"/>
-      <c r="I5" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="K5" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="L5" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="M5" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="N5" s="3" t="s">
+      <c r="E5" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="K5" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="L5" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="M5" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="N5" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="O5" s="3">
-        <v>1001</v>
+      <c r="O5" s="4" t="s">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells>
     <mergeCell ref="N1:AA1"/>
     <mergeCell ref="N2:AA2"/>
     <mergeCell ref="N3:AA3"/>
@@ -853,5 +858,6 @@
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/ProjectConfigTable/exgas_config/Datas/#exgas.ability.xlsx
+++ b/ProjectConfigTable/exgas_config/Datas/#exgas.ability.xlsx
@@ -146,7 +146,7 @@
     <t>ALApplyEffect</t>
   </si>
   <si>
-    <t>1002</t>
+    <t>1002;1001</t>
   </si>
 </sst>
 </file>

--- a/ProjectConfigTable/exgas_config/Datas/#exgas.ability.xlsx
+++ b/ProjectConfigTable/exgas_config/Datas/#exgas.ability.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
   <si>
     <t>##var</t>
   </si>
@@ -147,6 +147,24 @@
   </si>
   <si>
     <t>1002;1001</t>
+  </si>
+  <si>
+    <t>debug_ge_ability</t>
+  </si>
+  <si>
+    <t>调试GE</t>
+  </si>
+  <si>
+    <t>1003</t>
+  </si>
+  <si>
+    <t>debug_ge_2</t>
+  </si>
+  <si>
+    <t>调试ge2</t>
+  </si>
+  <si>
+    <t>1005</t>
   </si>
 </sst>
 </file>
@@ -274,11 +292,12 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
     <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
     <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
     <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
     <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
@@ -589,18 +608,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AA5"/>
+  <dimension ref="A1:AA7"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="4" max="5" width="15.33203125" customWidth="1" style="4"/>
-    <col min="6" max="6" width="16.109375" customWidth="1" style="4"/>
-    <col min="7" max="7" width="15.33203125" customWidth="1" style="4"/>
-    <col min="8" max="8" width="23.6640625" customWidth="1" style="4"/>
-    <col min="9" max="9" width="20" customWidth="1" style="4"/>
-    <col min="10" max="10" width="21.77734375" customWidth="1" style="4"/>
-    <col min="11" max="12" width="21" customWidth="1" style="4"/>
-    <col min="13" max="13" width="20.21875" customWidth="1" style="4"/>
-    <col min="14" max="14" width="16.109375" customWidth="1" style="3"/>
+    <col min="4" max="5" width="15.33203125" customWidth="1" style="5"/>
+    <col min="6" max="6" width="16.109375" customWidth="1" style="5"/>
+    <col min="7" max="7" width="15.33203125" customWidth="1" style="5"/>
+    <col min="8" max="8" width="23.6640625" customWidth="1" style="5"/>
+    <col min="9" max="9" width="20" customWidth="1" style="5"/>
+    <col min="10" max="10" width="21.77734375" customWidth="1" style="5"/>
+    <col min="11" max="12" width="21" customWidth="1" style="5"/>
+    <col min="13" max="13" width="20.21875" customWidth="1" style="5"/>
+    <col min="14" max="14" width="16.109375" customWidth="1" style="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="19.2">
@@ -625,40 +644,40 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="H1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="I1" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="7" t="s">
+      <c r="J1" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="7" t="s">
+      <c r="K1" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="7" t="s">
+      <c r="L1" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="7" t="s">
+      <c r="M1" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="9" t="s">
+      <c r="N1" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="10"/>
-      <c r="P1" s="10"/>
-      <c r="Q1" s="10"/>
-      <c r="R1" s="10"/>
-      <c r="S1" s="10"/>
-      <c r="T1" s="10"/>
-      <c r="U1" s="10"/>
-      <c r="V1" s="10"/>
-      <c r="W1" s="10"/>
-      <c r="X1" s="10"/>
-      <c r="Y1" s="10"/>
-      <c r="Z1" s="10"/>
-      <c r="AA1" s="11"/>
+      <c r="O1" s="11"/>
+      <c r="P1" s="11"/>
+      <c r="Q1" s="11"/>
+      <c r="R1" s="11"/>
+      <c r="S1" s="11"/>
+      <c r="T1" s="11"/>
+      <c r="U1" s="11"/>
+      <c r="V1" s="11"/>
+      <c r="W1" s="11"/>
+      <c r="X1" s="11"/>
+      <c r="Y1" s="11"/>
+      <c r="Z1" s="11"/>
+      <c r="AA1" s="12"/>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
@@ -682,40 +701,40 @@
       <c r="G2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="H2" s="8" t="s">
+      <c r="H2" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="I2" s="8" t="s">
+      <c r="I2" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="J2" s="8" t="s">
+      <c r="J2" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="K2" s="8" t="s">
+      <c r="K2" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="L2" s="8" t="s">
+      <c r="L2" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="M2" s="8" t="s">
+      <c r="M2" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="N2" s="9" t="s">
+      <c r="N2" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="O2" s="10"/>
-      <c r="P2" s="10"/>
-      <c r="Q2" s="10"/>
-      <c r="R2" s="10"/>
-      <c r="S2" s="10"/>
-      <c r="T2" s="10"/>
-      <c r="U2" s="10"/>
-      <c r="V2" s="10"/>
-      <c r="W2" s="10"/>
-      <c r="X2" s="10"/>
-      <c r="Y2" s="10"/>
-      <c r="Z2" s="10"/>
-      <c r="AA2" s="11"/>
+      <c r="O2" s="11"/>
+      <c r="P2" s="11"/>
+      <c r="Q2" s="11"/>
+      <c r="R2" s="11"/>
+      <c r="S2" s="11"/>
+      <c r="T2" s="11"/>
+      <c r="U2" s="11"/>
+      <c r="V2" s="11"/>
+      <c r="W2" s="11"/>
+      <c r="X2" s="11"/>
+      <c r="Y2" s="11"/>
+      <c r="Z2" s="11"/>
+      <c r="AA2" s="12"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
@@ -739,32 +758,32 @@
       <c r="G3" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="H3" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="N3" s="12" t="s">
+      <c r="N3" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="O3" s="13"/>
-      <c r="P3" s="13"/>
-      <c r="Q3" s="13"/>
-      <c r="R3" s="13"/>
-      <c r="S3" s="13"/>
-      <c r="T3" s="13"/>
-      <c r="U3" s="13"/>
-      <c r="V3" s="13"/>
-      <c r="W3" s="13"/>
-      <c r="X3" s="13"/>
-      <c r="Y3" s="13"/>
-      <c r="Z3" s="13"/>
-      <c r="AA3" s="14"/>
+      <c r="O3" s="14"/>
+      <c r="P3" s="14"/>
+      <c r="Q3" s="14"/>
+      <c r="R3" s="14"/>
+      <c r="S3" s="14"/>
+      <c r="T3" s="14"/>
+      <c r="U3" s="14"/>
+      <c r="V3" s="14"/>
+      <c r="W3" s="14"/>
+      <c r="X3" s="14"/>
+      <c r="Y3" s="14"/>
+      <c r="Z3" s="14"/>
+      <c r="AA3" s="15"/>
     </row>
     <row r="4">
       <c r="A4" s="1"/>
       <c r="B4" s="1">
         <v>10001</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="6" t="s">
         <v>27</v>
       </c>
       <c r="D4" s="1" t="s">
@@ -779,28 +798,28 @@
       <c r="G4" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="H4" s="5">
+      <c r="H4" s="6">
         <v>2002</v>
       </c>
-      <c r="I4" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="K4" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="L4" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="M4" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="N4" s="4" t="s">
+      <c r="I4" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J4" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="K4" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="L4" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="M4" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="N4" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="O4" s="3">
+      <c r="O4" s="4">
         <v>0.5</v>
       </c>
     </row>
@@ -809,44 +828,132 @@
       <c r="B5" s="1">
         <v>10002</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="6" t="s">
         <v>31</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E5" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="F5" s="5" t="s">
+      <c r="E5" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="F5" s="6" t="s">
         <v>29</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="H5" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="J5" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="K5" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="L5" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="M5" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="N5" s="4" t="s">
+      <c r="H5" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="J5" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="K5" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="L5" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="M5" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="N5" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="O5" s="4" t="s">
+      <c r="O5" s="5" t="s">
         <v>34</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="3">
+        <v>1003</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="J6" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="K6" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="L6" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="M6" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="N6" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="O6" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="2">
+        <v>1005</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="J7" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="K7" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="L7" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="M7" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="N7" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="O7" s="2" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>

--- a/ProjectConfigTable/exgas_config/Datas/#exgas.ability.xlsx
+++ b/ProjectConfigTable/exgas_config/Datas/#exgas.ability.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
   <si>
     <t>##var</t>
   </si>
@@ -132,6 +132,12 @@
   </si>
   <si>
     <t/>
+  </si>
+  <si>
+    <t>2002</t>
+  </si>
+  <si>
+    <t>3001</t>
   </si>
   <si>
     <t>ALMove</t>
@@ -292,11 +298,12 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
     <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
     <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
     <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
     <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
@@ -611,15 +618,15 @@
   <dimension ref="A1:AA7"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="4" max="5" width="15.33203125" customWidth="1" style="5"/>
-    <col min="6" max="6" width="16.109375" customWidth="1" style="5"/>
-    <col min="7" max="7" width="15.33203125" customWidth="1" style="5"/>
-    <col min="8" max="8" width="23.6640625" customWidth="1" style="5"/>
-    <col min="9" max="9" width="20" customWidth="1" style="5"/>
-    <col min="10" max="10" width="21.77734375" customWidth="1" style="5"/>
-    <col min="11" max="12" width="21" customWidth="1" style="5"/>
-    <col min="13" max="13" width="20.21875" customWidth="1" style="5"/>
-    <col min="14" max="14" width="16.109375" customWidth="1" style="4"/>
+    <col min="4" max="5" width="15.33203125" customWidth="1" style="6"/>
+    <col min="6" max="6" width="16.109375" customWidth="1" style="6"/>
+    <col min="7" max="7" width="15.33203125" customWidth="1" style="6"/>
+    <col min="8" max="8" width="23.6640625" customWidth="1" style="6"/>
+    <col min="9" max="9" width="20" customWidth="1" style="6"/>
+    <col min="10" max="10" width="21.77734375" customWidth="1" style="6"/>
+    <col min="11" max="12" width="21" customWidth="1" style="6"/>
+    <col min="13" max="13" width="20.21875" customWidth="1" style="6"/>
+    <col min="14" max="14" width="16.109375" customWidth="1" style="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="19.2">
@@ -644,40 +651,40 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="H1" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="8" t="s">
+      <c r="I1" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="8" t="s">
+      <c r="J1" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="8" t="s">
+      <c r="K1" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="8" t="s">
+      <c r="L1" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="8" t="s">
+      <c r="M1" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="10" t="s">
+      <c r="N1" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="11"/>
-      <c r="P1" s="11"/>
-      <c r="Q1" s="11"/>
-      <c r="R1" s="11"/>
-      <c r="S1" s="11"/>
-      <c r="T1" s="11"/>
-      <c r="U1" s="11"/>
-      <c r="V1" s="11"/>
-      <c r="W1" s="11"/>
-      <c r="X1" s="11"/>
-      <c r="Y1" s="11"/>
-      <c r="Z1" s="11"/>
-      <c r="AA1" s="12"/>
+      <c r="O1" s="12"/>
+      <c r="P1" s="12"/>
+      <c r="Q1" s="12"/>
+      <c r="R1" s="12"/>
+      <c r="S1" s="12"/>
+      <c r="T1" s="12"/>
+      <c r="U1" s="12"/>
+      <c r="V1" s="12"/>
+      <c r="W1" s="12"/>
+      <c r="X1" s="12"/>
+      <c r="Y1" s="12"/>
+      <c r="Z1" s="12"/>
+      <c r="AA1" s="13"/>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
@@ -701,40 +708,40 @@
       <c r="G2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="H2" s="9" t="s">
+      <c r="H2" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="I2" s="9" t="s">
+      <c r="I2" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="J2" s="9" t="s">
+      <c r="J2" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="K2" s="9" t="s">
+      <c r="K2" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="L2" s="9" t="s">
+      <c r="L2" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="M2" s="9" t="s">
+      <c r="M2" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="N2" s="10" t="s">
+      <c r="N2" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="O2" s="11"/>
-      <c r="P2" s="11"/>
-      <c r="Q2" s="11"/>
-      <c r="R2" s="11"/>
-      <c r="S2" s="11"/>
-      <c r="T2" s="11"/>
-      <c r="U2" s="11"/>
-      <c r="V2" s="11"/>
-      <c r="W2" s="11"/>
-      <c r="X2" s="11"/>
-      <c r="Y2" s="11"/>
-      <c r="Z2" s="11"/>
-      <c r="AA2" s="12"/>
+      <c r="O2" s="12"/>
+      <c r="P2" s="12"/>
+      <c r="Q2" s="12"/>
+      <c r="R2" s="12"/>
+      <c r="S2" s="12"/>
+      <c r="T2" s="12"/>
+      <c r="U2" s="12"/>
+      <c r="V2" s="12"/>
+      <c r="W2" s="12"/>
+      <c r="X2" s="12"/>
+      <c r="Y2" s="12"/>
+      <c r="Z2" s="12"/>
+      <c r="AA2" s="13"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
@@ -758,32 +765,32 @@
       <c r="G3" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="H3" s="6" t="s">
+      <c r="H3" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="N3" s="13" t="s">
+      <c r="N3" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="O3" s="14"/>
-      <c r="P3" s="14"/>
-      <c r="Q3" s="14"/>
-      <c r="R3" s="14"/>
-      <c r="S3" s="14"/>
-      <c r="T3" s="14"/>
-      <c r="U3" s="14"/>
-      <c r="V3" s="14"/>
-      <c r="W3" s="14"/>
-      <c r="X3" s="14"/>
-      <c r="Y3" s="14"/>
-      <c r="Z3" s="14"/>
-      <c r="AA3" s="15"/>
+      <c r="O3" s="15"/>
+      <c r="P3" s="15"/>
+      <c r="Q3" s="15"/>
+      <c r="R3" s="15"/>
+      <c r="S3" s="15"/>
+      <c r="T3" s="15"/>
+      <c r="U3" s="15"/>
+      <c r="V3" s="15"/>
+      <c r="W3" s="15"/>
+      <c r="X3" s="15"/>
+      <c r="Y3" s="15"/>
+      <c r="Z3" s="15"/>
+      <c r="AA3" s="16"/>
     </row>
     <row r="4">
       <c r="A4" s="1"/>
       <c r="B4" s="1">
         <v>10001</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="7" t="s">
         <v>27</v>
       </c>
       <c r="D4" s="1" t="s">
@@ -798,28 +805,28 @@
       <c r="G4" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="H4" s="6">
-        <v>2002</v>
-      </c>
-      <c r="I4" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="J4" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="K4" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="L4" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="M4" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="N4" s="5" t="s">
+      <c r="H4" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="O4" s="4">
+      <c r="I4" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="J4" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="K4" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="L4" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="M4" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="N4" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="O4" s="5">
         <v>0.5</v>
       </c>
     </row>
@@ -828,132 +835,132 @@
       <c r="B5" s="1">
         <v>10002</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H5" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="I5" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J5" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="K5" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="L5" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="D5" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="H5" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="I5" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="J5" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="K5" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="L5" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="M5" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="N5" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="O5" s="5" t="s">
-        <v>34</v>
+      <c r="M5" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="N5" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="O5" s="6" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="3">
+      <c r="B6" s="4">
         <v>1003</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J6" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="K6" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="L6" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="M6" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="N6" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="D6" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="H6" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="I6" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="J6" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="K6" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="L6" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="M6" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="N6" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="O6" s="3" t="s">
-        <v>37</v>
+      <c r="O6" s="4" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="2">
+      <c r="B7" s="3">
         <v>1005</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="H7" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="I7" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="J7" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="K7" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="L7" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="M7" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="N7" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="O7" s="2" t="s">
+      <c r="C7" s="3" t="s">
         <v>40</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="H7" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="I7" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J7" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="K7" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="L7" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="M7" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="N7" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="O7" s="3" t="s">
+        <v>42</v>
       </c>
     </row>
   </sheetData>

--- a/ProjectConfigTable/exgas_config/Datas/#exgas.ability.xlsx
+++ b/ProjectConfigTable/exgas_config/Datas/#exgas.ability.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="47">
   <si>
     <t>##var</t>
   </si>
@@ -171,6 +171,18 @@
   </si>
   <si>
     <t>1005</t>
+  </si>
+  <si>
+    <t>Attack</t>
+  </si>
+  <si>
+    <t>玩家普通攻击</t>
+  </si>
+  <si>
+    <t>3003</t>
+  </si>
+  <si>
+    <t>ALTimeline</t>
   </si>
 </sst>
 </file>
@@ -298,11 +310,12 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
     <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
     <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
     <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
     <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
@@ -615,18 +628,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AA7"/>
+  <dimension ref="A1:AA8"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="4" max="5" width="15.33203125" customWidth="1" style="6"/>
-    <col min="6" max="6" width="16.109375" customWidth="1" style="6"/>
-    <col min="7" max="7" width="15.33203125" customWidth="1" style="6"/>
-    <col min="8" max="8" width="23.6640625" customWidth="1" style="6"/>
-    <col min="9" max="9" width="20" customWidth="1" style="6"/>
-    <col min="10" max="10" width="21.77734375" customWidth="1" style="6"/>
-    <col min="11" max="12" width="21" customWidth="1" style="6"/>
-    <col min="13" max="13" width="20.21875" customWidth="1" style="6"/>
-    <col min="14" max="14" width="16.109375" customWidth="1" style="5"/>
+    <col min="4" max="5" width="15.33203125" customWidth="1" style="7"/>
+    <col min="6" max="6" width="16.109375" customWidth="1" style="7"/>
+    <col min="7" max="7" width="15.33203125" customWidth="1" style="7"/>
+    <col min="8" max="8" width="23.6640625" customWidth="1" style="7"/>
+    <col min="9" max="9" width="20" customWidth="1" style="7"/>
+    <col min="10" max="10" width="21.77734375" customWidth="1" style="7"/>
+    <col min="11" max="12" width="21" customWidth="1" style="7"/>
+    <col min="13" max="13" width="20.21875" customWidth="1" style="7"/>
+    <col min="14" max="14" width="16.109375" customWidth="1" style="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="19.2">
@@ -651,40 +664,40 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="H1" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="I1" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="9" t="s">
+      <c r="J1" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="9" t="s">
+      <c r="K1" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="9" t="s">
+      <c r="L1" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="9" t="s">
+      <c r="M1" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="11" t="s">
+      <c r="N1" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="12"/>
-      <c r="P1" s="12"/>
-      <c r="Q1" s="12"/>
-      <c r="R1" s="12"/>
-      <c r="S1" s="12"/>
-      <c r="T1" s="12"/>
-      <c r="U1" s="12"/>
-      <c r="V1" s="12"/>
-      <c r="W1" s="12"/>
-      <c r="X1" s="12"/>
-      <c r="Y1" s="12"/>
-      <c r="Z1" s="12"/>
-      <c r="AA1" s="13"/>
+      <c r="O1" s="13"/>
+      <c r="P1" s="13"/>
+      <c r="Q1" s="13"/>
+      <c r="R1" s="13"/>
+      <c r="S1" s="13"/>
+      <c r="T1" s="13"/>
+      <c r="U1" s="13"/>
+      <c r="V1" s="13"/>
+      <c r="W1" s="13"/>
+      <c r="X1" s="13"/>
+      <c r="Y1" s="13"/>
+      <c r="Z1" s="13"/>
+      <c r="AA1" s="14"/>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
@@ -708,40 +721,40 @@
       <c r="G2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="H2" s="10" t="s">
+      <c r="H2" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="I2" s="10" t="s">
+      <c r="I2" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="J2" s="10" t="s">
+      <c r="J2" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="K2" s="10" t="s">
+      <c r="K2" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="L2" s="10" t="s">
+      <c r="L2" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="M2" s="10" t="s">
+      <c r="M2" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="N2" s="11" t="s">
+      <c r="N2" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="O2" s="12"/>
-      <c r="P2" s="12"/>
-      <c r="Q2" s="12"/>
-      <c r="R2" s="12"/>
-      <c r="S2" s="12"/>
-      <c r="T2" s="12"/>
-      <c r="U2" s="12"/>
-      <c r="V2" s="12"/>
-      <c r="W2" s="12"/>
-      <c r="X2" s="12"/>
-      <c r="Y2" s="12"/>
-      <c r="Z2" s="12"/>
-      <c r="AA2" s="13"/>
+      <c r="O2" s="13"/>
+      <c r="P2" s="13"/>
+      <c r="Q2" s="13"/>
+      <c r="R2" s="13"/>
+      <c r="S2" s="13"/>
+      <c r="T2" s="13"/>
+      <c r="U2" s="13"/>
+      <c r="V2" s="13"/>
+      <c r="W2" s="13"/>
+      <c r="X2" s="13"/>
+      <c r="Y2" s="13"/>
+      <c r="Z2" s="13"/>
+      <c r="AA2" s="14"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
@@ -765,32 +778,32 @@
       <c r="G3" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="H3" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="N3" s="14" t="s">
+      <c r="N3" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="O3" s="15"/>
-      <c r="P3" s="15"/>
-      <c r="Q3" s="15"/>
-      <c r="R3" s="15"/>
-      <c r="S3" s="15"/>
-      <c r="T3" s="15"/>
-      <c r="U3" s="15"/>
-      <c r="V3" s="15"/>
-      <c r="W3" s="15"/>
-      <c r="X3" s="15"/>
-      <c r="Y3" s="15"/>
-      <c r="Z3" s="15"/>
-      <c r="AA3" s="16"/>
+      <c r="O3" s="16"/>
+      <c r="P3" s="16"/>
+      <c r="Q3" s="16"/>
+      <c r="R3" s="16"/>
+      <c r="S3" s="16"/>
+      <c r="T3" s="16"/>
+      <c r="U3" s="16"/>
+      <c r="V3" s="16"/>
+      <c r="W3" s="16"/>
+      <c r="X3" s="16"/>
+      <c r="Y3" s="16"/>
+      <c r="Z3" s="16"/>
+      <c r="AA3" s="17"/>
     </row>
     <row r="4">
       <c r="A4" s="1"/>
       <c r="B4" s="1">
         <v>10001</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="8" t="s">
         <v>27</v>
       </c>
       <c r="D4" s="1" t="s">
@@ -805,28 +818,28 @@
       <c r="G4" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="H4" s="7" t="s">
+      <c r="H4" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="I4" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="J4" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="K4" s="6" t="s">
+      <c r="I4" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="J4" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="K4" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="L4" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="M4" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="N4" s="6" t="s">
+      <c r="L4" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="M4" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="N4" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="O4" s="5">
+      <c r="O4" s="6">
         <v>0.5</v>
       </c>
     </row>
@@ -835,132 +848,173 @@
       <c r="B5" s="1">
         <v>10002</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="8" t="s">
         <v>33</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="E5" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="F5" s="7" t="s">
+      <c r="E5" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="F5" s="8" t="s">
         <v>29</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="H5" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="I5" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="J5" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="K5" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="L5" s="6" t="s">
+      <c r="H5" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="I5" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="J5" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="K5" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="L5" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="M5" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="N5" s="6" t="s">
+      <c r="M5" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="N5" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="O5" s="6" t="s">
+      <c r="O5" s="7" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="4">
+      <c r="B6" s="5">
         <v>1003</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="E6" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="G6" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="H6" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="I6" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="J6" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="K6" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="L6" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="M6" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="N6" s="5" t="s">
+      <c r="E6" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="H6" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="I6" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="J6" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="K6" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="L6" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="M6" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="N6" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="O6" s="4" t="s">
+      <c r="O6" s="5" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="3">
+      <c r="B7" s="4">
         <v>1005</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D7" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="E7" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="G7" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="H7" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="I7" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="J7" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="K7" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="L7" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="M7" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="N7" s="5" t="s">
+      <c r="E7" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="H7" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="I7" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="J7" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="K7" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="L7" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="M7" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="N7" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="O7" s="3" t="s">
+      <c r="O7" s="4" t="s">
         <v>42</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="3">
+        <v>20001</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="H8" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="I8" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="J8" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="K8" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="L8" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="M8" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="N8" s="6" t="s">
+        <v>46</v>
       </c>
     </row>
   </sheetData>

--- a/ProjectConfigTable/exgas_config/Datas/#exgas.ability.xlsx
+++ b/ProjectConfigTable/exgas_config/Datas/#exgas.ability.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\MyRepo\gameplay-ability-system-for-unity\ProjectConfigTable\exgas_config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD78F964-1011-42B3-8A57-266E772E42CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E0AAABE-5E37-425B-9FC2-7F8126CC5F77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913" fullCalcOnLoad="1"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="47">
   <si>
     <t>##var</t>
   </si>
@@ -81,10 +81,10 @@
     <t>string</t>
   </si>
   <si>
-    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+    <r>
       <t>(list#sep=;</t>
     </r>
-    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+    <r>
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
@@ -95,7 +95,7 @@
       </rPr>
       <t>),int</t>
     </r>
-    <phoneticPr xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" fontId="4" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>AbilityLogic?</t>
@@ -189,8 +189,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -223,6 +222,14 @@
       <color rgb="FF1F2328"/>
       <name val="Segoe UI"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -310,47 +317,46 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
+  <cellXfs count="17">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="3" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="4" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="2" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="2" applyFont="1" fillId="0" applyFill="1" borderId="1" applyBorder="1" xfId="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="2" applyFont="1" fillId="0" applyFill="1" borderId="2" applyBorder="1" xfId="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="2" applyFont="1" fillId="0" applyFill="1" borderId="3" applyBorder="1" xfId="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="2" applyFont="1" fillId="0" applyFill="1" borderId="4" applyBorder="1" xfId="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="2" applyFont="1" fillId="0" applyFill="1" borderId="5" applyBorder="1" xfId="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="2" applyFont="1" fillId="0" applyFill="1" borderId="6" applyBorder="1" xfId="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 2" xfId="1"/>
+    <cellStyle name="常规 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -631,18 +637,18 @@
   <dimension ref="A1:AA8"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="4" max="5" width="15.33203125" customWidth="1" style="7"/>
-    <col min="6" max="6" width="16.109375" customWidth="1" style="7"/>
-    <col min="7" max="7" width="15.33203125" customWidth="1" style="7"/>
-    <col min="8" max="8" width="23.6640625" customWidth="1" style="7"/>
-    <col min="9" max="9" width="20" customWidth="1" style="7"/>
-    <col min="10" max="10" width="21.77734375" customWidth="1" style="7"/>
-    <col min="11" max="12" width="21" customWidth="1" style="7"/>
-    <col min="13" max="13" width="20.21875" customWidth="1" style="7"/>
-    <col min="14" max="14" width="16.109375" customWidth="1" style="6"/>
+    <col min="4" max="5" width="15.33203125" style="6" customWidth="1"/>
+    <col min="6" max="6" width="16.109375" style="6" customWidth="1"/>
+    <col min="7" max="7" width="15.33203125" style="6" customWidth="1"/>
+    <col min="8" max="8" width="23.6640625" style="6" customWidth="1"/>
+    <col min="9" max="9" width="20" style="6" customWidth="1"/>
+    <col min="10" max="10" width="21.77734375" style="6" customWidth="1"/>
+    <col min="11" max="12" width="21" style="6" customWidth="1"/>
+    <col min="13" max="13" width="20.21875" style="6" customWidth="1"/>
+    <col min="14" max="14" width="16.109375" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="19.2">
+    <row r="1" spans="1:27" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -664,42 +670,42 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="H1" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="10" t="s">
+      <c r="I1" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="10" t="s">
+      <c r="J1" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="10" t="s">
+      <c r="K1" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="10" t="s">
+      <c r="L1" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="10" t="s">
+      <c r="M1" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="12" t="s">
+      <c r="N1" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="13"/>
-      <c r="P1" s="13"/>
-      <c r="Q1" s="13"/>
-      <c r="R1" s="13"/>
-      <c r="S1" s="13"/>
-      <c r="T1" s="13"/>
-      <c r="U1" s="13"/>
-      <c r="V1" s="13"/>
-      <c r="W1" s="13"/>
-      <c r="X1" s="13"/>
-      <c r="Y1" s="13"/>
-      <c r="Z1" s="13"/>
-      <c r="AA1" s="14"/>
+      <c r="O1" s="12"/>
+      <c r="P1" s="12"/>
+      <c r="Q1" s="12"/>
+      <c r="R1" s="12"/>
+      <c r="S1" s="12"/>
+      <c r="T1" s="12"/>
+      <c r="U1" s="12"/>
+      <c r="V1" s="12"/>
+      <c r="W1" s="12"/>
+      <c r="X1" s="12"/>
+      <c r="Y1" s="12"/>
+      <c r="Z1" s="12"/>
+      <c r="AA1" s="13"/>
     </row>
-    <row r="2">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>14</v>
       </c>
@@ -721,42 +727,42 @@
       <c r="G2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="H2" s="11" t="s">
+      <c r="H2" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="I2" s="11" t="s">
+      <c r="I2" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="J2" s="11" t="s">
+      <c r="J2" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="K2" s="11" t="s">
+      <c r="K2" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="L2" s="11" t="s">
+      <c r="L2" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="M2" s="11" t="s">
+      <c r="M2" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="N2" s="12" t="s">
+      <c r="N2" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="O2" s="13"/>
-      <c r="P2" s="13"/>
-      <c r="Q2" s="13"/>
-      <c r="R2" s="13"/>
-      <c r="S2" s="13"/>
-      <c r="T2" s="13"/>
-      <c r="U2" s="13"/>
-      <c r="V2" s="13"/>
-      <c r="W2" s="13"/>
-      <c r="X2" s="13"/>
-      <c r="Y2" s="13"/>
-      <c r="Z2" s="13"/>
-      <c r="AA2" s="14"/>
+      <c r="O2" s="12"/>
+      <c r="P2" s="12"/>
+      <c r="Q2" s="12"/>
+      <c r="R2" s="12"/>
+      <c r="S2" s="12"/>
+      <c r="T2" s="12"/>
+      <c r="U2" s="12"/>
+      <c r="V2" s="12"/>
+      <c r="W2" s="12"/>
+      <c r="X2" s="12"/>
+      <c r="Y2" s="12"/>
+      <c r="Z2" s="12"/>
+      <c r="AA2" s="13"/>
     </row>
-    <row r="3">
+    <row r="3" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>19</v>
       </c>
@@ -778,32 +784,32 @@
       <c r="G3" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="H3" s="8" t="s">
+      <c r="H3" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="N3" s="15" t="s">
+      <c r="N3" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="O3" s="16"/>
-      <c r="P3" s="16"/>
-      <c r="Q3" s="16"/>
-      <c r="R3" s="16"/>
-      <c r="S3" s="16"/>
-      <c r="T3" s="16"/>
-      <c r="U3" s="16"/>
-      <c r="V3" s="16"/>
-      <c r="W3" s="16"/>
-      <c r="X3" s="16"/>
-      <c r="Y3" s="16"/>
-      <c r="Z3" s="16"/>
-      <c r="AA3" s="17"/>
+      <c r="O3" s="15"/>
+      <c r="P3" s="15"/>
+      <c r="Q3" s="15"/>
+      <c r="R3" s="15"/>
+      <c r="S3" s="15"/>
+      <c r="T3" s="15"/>
+      <c r="U3" s="15"/>
+      <c r="V3" s="15"/>
+      <c r="W3" s="15"/>
+      <c r="X3" s="15"/>
+      <c r="Y3" s="15"/>
+      <c r="Z3" s="15"/>
+      <c r="AA3" s="16"/>
     </row>
-    <row r="4">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="1">
         <v>10001</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="7" t="s">
         <v>27</v>
       </c>
       <c r="D4" s="1" t="s">
@@ -818,207 +824,210 @@
       <c r="G4" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="H4" s="8" t="s">
+      <c r="H4" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="I4" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="J4" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="K4" s="7" t="s">
+      <c r="I4" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="J4" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="K4" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="L4" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="M4" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="N4" s="7" t="s">
+      <c r="L4" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="M4" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="N4" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="O4" s="6">
+      <c r="O4" s="5">
         <v>0.5</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" s="1">
         <v>10002</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="7" t="s">
         <v>33</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="E5" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="F5" s="8" t="s">
+      <c r="E5" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="F5" s="7" t="s">
         <v>29</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="H5" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="I5" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="J5" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="K5" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="L5" s="7" t="s">
+      <c r="H5" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="I5" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J5" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="K5" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="L5" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="M5" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="N5" s="7" t="s">
+      <c r="M5" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="N5" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="O5" s="7" t="s">
+      <c r="O5" s="6" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="6">
-      <c r="B6" s="5">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="B6" s="4">
         <v>1003</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="E6" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="G6" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="H6" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="I6" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="J6" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="K6" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="L6" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="M6" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="N6" s="6" t="s">
+      <c r="E6" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J6" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="K6" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="L6" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="M6" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="N6" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="O6" s="5" t="s">
+      <c r="O6" s="4" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="7">
-      <c r="B7" s="4">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="B7" s="3">
         <v>1005</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D7" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="E7" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="G7" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="H7" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="I7" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="J7" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="K7" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="L7" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="M7" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="N7" s="6" t="s">
+      <c r="E7" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="H7" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="I7" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J7" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="K7" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="L7" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="M7" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="N7" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="O7" s="4" t="s">
+      <c r="O7" s="3" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="8">
-      <c r="B8" s="3">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="B8" s="2">
         <v>20001</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="D8" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="E8" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="G8" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="H8" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="I8" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="J8" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="K8" s="7" t="s">
+      <c r="E8" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="H8" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="I8" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J8" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="K8" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="L8" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="M8" s="7" t="s">
+      <c r="L8" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="M8" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="N8" s="6" t="s">
+      <c r="N8" s="5" t="s">
         <v>46</v>
+      </c>
+      <c r="O8">
+        <v>101</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells>
+  <mergeCells count="3">
     <mergeCell ref="N1:AA1"/>
     <mergeCell ref="N2:AA2"/>
     <mergeCell ref="N3:AA3"/>
@@ -1026,6 +1035,5 @@
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/ProjectConfigTable/exgas_config/Datas/#exgas.ability.xlsx
+++ b/ProjectConfigTable/exgas_config/Datas/#exgas.ability.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\MyRepo\gameplay-ability-system-for-unity\ProjectConfigTable\exgas_config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E0AAABE-5E37-425B-9FC2-7F8126CC5F77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F7579C0-2C5B-4B47-ABBC-36AC58E75728}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -98,9 +98,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>AbilityLogic?</t>
-  </si>
-  <si>
     <t>##</t>
   </si>
   <si>
@@ -122,67 +119,72 @@
     <t>描述标签</t>
   </si>
   <si>
+    <t>move</t>
+  </si>
+  <si>
+    <t>移动</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>2002</t>
+  </si>
+  <si>
+    <t>3001</t>
+  </si>
+  <si>
+    <t>ALMove</t>
+  </si>
+  <si>
+    <t>RunSpeedUp</t>
+  </si>
+  <si>
+    <t>加速</t>
+  </si>
+  <si>
+    <t>ALApplyEffect</t>
+  </si>
+  <si>
+    <t>1002;1001</t>
+  </si>
+  <si>
+    <t>debug_ge_ability</t>
+  </si>
+  <si>
+    <t>调试GE</t>
+  </si>
+  <si>
+    <t>1003</t>
+  </si>
+  <si>
+    <t>debug_ge_2</t>
+  </si>
+  <si>
+    <t>调试ge2</t>
+  </si>
+  <si>
+    <t>1005</t>
+  </si>
+  <si>
+    <t>Attack</t>
+  </si>
+  <si>
+    <t>玩家普通攻击</t>
+  </si>
+  <si>
+    <t>3003</t>
+  </si>
+  <si>
+    <t>ALTimeline</t>
+  </si>
+  <si>
+    <t>AbilityLogic</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>技能逻辑：支持多态，添加新AbilityLogic类型去__bean__中添加即可。暂定给了13个变量的预留位，不够的话就自己加长。</t>
-  </si>
-  <si>
-    <t>move</t>
-  </si>
-  <si>
-    <t>移动</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>2002</t>
-  </si>
-  <si>
-    <t>3001</t>
-  </si>
-  <si>
-    <t>ALMove</t>
-  </si>
-  <si>
-    <t>RunSpeedUp</t>
-  </si>
-  <si>
-    <t>加速</t>
-  </si>
-  <si>
-    <t>ALApplyEffect</t>
-  </si>
-  <si>
-    <t>1002;1001</t>
-  </si>
-  <si>
-    <t>debug_ge_ability</t>
-  </si>
-  <si>
-    <t>调试GE</t>
-  </si>
-  <si>
-    <t>1003</t>
-  </si>
-  <si>
-    <t>debug_ge_2</t>
-  </si>
-  <si>
-    <t>调试ge2</t>
-  </si>
-  <si>
-    <t>1005</t>
-  </si>
-  <si>
-    <t>Attack</t>
-  </si>
-  <si>
-    <t>玩家普通攻击</t>
-  </si>
-  <si>
-    <t>3003</t>
-  </si>
-  <si>
-    <t>ALTimeline</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -317,7 +319,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
@@ -344,13 +346,16 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -745,8 +750,8 @@
       <c r="M2" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="N2" s="11" t="s">
-        <v>18</v>
+      <c r="N2" s="16" t="s">
+        <v>45</v>
       </c>
       <c r="O2" s="12"/>
       <c r="P2" s="12"/>
@@ -764,45 +769,45 @@
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="H3" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="H3" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="N3" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="O3" s="15"/>
-      <c r="P3" s="15"/>
-      <c r="Q3" s="15"/>
-      <c r="R3" s="15"/>
-      <c r="S3" s="15"/>
-      <c r="T3" s="15"/>
-      <c r="U3" s="15"/>
-      <c r="V3" s="15"/>
-      <c r="W3" s="15"/>
-      <c r="X3" s="15"/>
-      <c r="Y3" s="15"/>
-      <c r="Z3" s="15"/>
-      <c r="AA3" s="16"/>
+      <c r="N3" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="O3" s="14"/>
+      <c r="P3" s="14"/>
+      <c r="Q3" s="14"/>
+      <c r="R3" s="14"/>
+      <c r="S3" s="14"/>
+      <c r="T3" s="14"/>
+      <c r="U3" s="14"/>
+      <c r="V3" s="14"/>
+      <c r="W3" s="14"/>
+      <c r="X3" s="14"/>
+      <c r="Y3" s="14"/>
+      <c r="Z3" s="14"/>
+      <c r="AA3" s="15"/>
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -810,40 +815,40 @@
         <v>10001</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D4" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H4" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="I4" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="J4" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="K4" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="F4" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="H4" s="7" t="s">
+      <c r="L4" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="M4" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="N4" s="6" t="s">
         <v>30</v>
-      </c>
-      <c r="I4" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="J4" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="K4" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="L4" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="M4" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="N4" s="6" t="s">
-        <v>32</v>
       </c>
       <c r="O4" s="5">
         <v>0.5</v>
@@ -855,43 +860,43 @@
         <v>10002</v>
       </c>
       <c r="C5" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H5" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="I5" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="J5" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="K5" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="L5" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="M5" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="N5" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="O5" s="6" t="s">
         <v>34</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="H5" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="I5" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="J5" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="K5" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="L5" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="M5" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="N5" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="O5" s="6" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="6" spans="1:27" x14ac:dyDescent="0.25">
@@ -899,43 +904,43 @@
         <v>1003</v>
       </c>
       <c r="C6" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="J6" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="K6" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="L6" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="M6" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="N6" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="O6" s="4" t="s">
         <v>37</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="G6" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="H6" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="I6" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="J6" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="K6" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="L6" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="M6" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="N6" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="O6" s="4" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="7" spans="1:27" x14ac:dyDescent="0.25">
@@ -943,43 +948,43 @@
         <v>1005</v>
       </c>
       <c r="C7" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H7" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="I7" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="J7" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="K7" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="L7" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="M7" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="N7" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="O7" s="3" t="s">
         <v>40</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="G7" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="H7" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="I7" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="J7" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="K7" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="L7" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="M7" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="N7" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="O7" s="3" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="8" spans="1:27" x14ac:dyDescent="0.25">
@@ -987,40 +992,40 @@
         <v>20001</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H8" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="I8" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="J8" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="K8" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="L8" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="M8" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="N8" s="5" t="s">
         <v>44</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="G8" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="H8" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="I8" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="J8" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="K8" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="L8" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="M8" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="N8" s="5" t="s">
-        <v>46</v>
       </c>
       <c r="O8">
         <v>101</v>

--- a/ProjectConfigTable/exgas_config/Datas/#exgas.ability.xlsx
+++ b/ProjectConfigTable/exgas_config/Datas/#exgas.ability.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\MyRepo\gameplay-ability-system-for-unity\ProjectConfigTable\exgas_config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F7579C0-2C5B-4B47-ABBC-36AC58E75728}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6675D134-DD69-464F-80CC-3EA49DC0FBFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,48 +28,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="48">
   <si>
     <t>##var</t>
   </si>
   <si>
     <t>id</t>
-  </si>
-  <si>
-    <t>name</t>
-  </si>
-  <si>
-    <t>desc</t>
-  </si>
-  <si>
-    <t>cost</t>
-  </si>
-  <si>
-    <t>cdEffect</t>
-  </si>
-  <si>
-    <t>cd</t>
-  </si>
-  <si>
-    <t>assetTags</t>
-  </si>
-  <si>
-    <t>cancelAbilityWithTags</t>
-  </si>
-  <si>
-    <t>blockAbilityWithTags</t>
-  </si>
-  <si>
-    <t>activationOwnedTags</t>
-  </si>
-  <si>
-    <t>activationRequiredTags</t>
-  </si>
-  <si>
-    <t>activationBlockedTags</t>
-  </si>
-  <si>
-    <t>abilityLogic</t>
   </si>
   <si>
     <t>##type</t>
@@ -98,6 +62,9 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
+    <t>AbilityLogic</t>
+  </si>
+  <si>
     <t>##</t>
   </si>
   <si>
@@ -119,6 +86,9 @@
     <t>描述标签</t>
   </si>
   <si>
+    <t>技能逻辑：支持多态，添加新AbilityLogic类型去__bean__中添加即可。暂定给了13个变量的预留位，不够的话就自己加长。</t>
+  </si>
+  <si>
     <t>move</t>
   </si>
   <si>
@@ -183,7 +153,51 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>技能逻辑：支持多态，添加新AbilityLogic类型去__bean__中添加即可。暂定给了13个变量的预留位，不够的话就自己加长。</t>
+    <t>ActivationBlockedTags</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ID</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Name</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Desc</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cost</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>CdEffect</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cd</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>AssetTags</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>CancelAbilityWithTags</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>BlockAbilityWithTags</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ActivationOwnedTags</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ActivationRequiredTags</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -329,6 +343,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -337,25 +352,22 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -642,15 +654,15 @@
   <dimension ref="A1:AA8"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="4" max="5" width="15.33203125" style="6" customWidth="1"/>
-    <col min="6" max="6" width="16.109375" style="6" customWidth="1"/>
-    <col min="7" max="7" width="15.33203125" style="6" customWidth="1"/>
-    <col min="8" max="8" width="23.6640625" style="6" customWidth="1"/>
-    <col min="9" max="9" width="20" style="6" customWidth="1"/>
-    <col min="10" max="10" width="21.77734375" style="6" customWidth="1"/>
-    <col min="11" max="12" width="21" style="6" customWidth="1"/>
-    <col min="13" max="13" width="20.21875" style="6" customWidth="1"/>
-    <col min="14" max="14" width="16.109375" style="5" customWidth="1"/>
+    <col min="4" max="5" width="15.33203125" style="7" customWidth="1"/>
+    <col min="6" max="6" width="16.109375" style="7" customWidth="1"/>
+    <col min="7" max="7" width="15.33203125" style="7" customWidth="1"/>
+    <col min="8" max="8" width="23.6640625" style="7" customWidth="1"/>
+    <col min="9" max="9" width="20" style="7" customWidth="1"/>
+    <col min="10" max="10" width="21.77734375" style="7" customWidth="1"/>
+    <col min="11" max="12" width="21" style="7" customWidth="1"/>
+    <col min="13" max="13" width="20.21875" style="7" customWidth="1"/>
+    <col min="14" max="14" width="16.109375" style="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:27" ht="19.2" x14ac:dyDescent="0.45">
@@ -658,43 +670,43 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>37</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2</v>
+        <v>38</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>3</v>
+        <v>39</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>5</v>
+        <v>41</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="11" t="s">
-        <v>13</v>
+        <v>42</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="J1" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="K1" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="L1" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="M1" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="N1" s="14" t="s">
+        <v>35</v>
       </c>
       <c r="O1" s="12"/>
       <c r="P1" s="12"/>
@@ -712,46 +724,46 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H2" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="I2" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="J2" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="K2" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="L2" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="M2" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="N2" s="16" t="s">
-        <v>45</v>
+        <v>3</v>
+      </c>
+      <c r="H2" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="I2" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="J2" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="K2" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="L2" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="M2" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="N2" s="14" t="s">
+        <v>6</v>
       </c>
       <c r="O2" s="12"/>
       <c r="P2" s="12"/>
@@ -769,88 +781,88 @@
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="H3" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="N3" s="17" t="s">
-        <v>46</v>
-      </c>
-      <c r="O3" s="14"/>
-      <c r="P3" s="14"/>
-      <c r="Q3" s="14"/>
-      <c r="R3" s="14"/>
-      <c r="S3" s="14"/>
-      <c r="T3" s="14"/>
-      <c r="U3" s="14"/>
-      <c r="V3" s="14"/>
-      <c r="W3" s="14"/>
-      <c r="X3" s="14"/>
-      <c r="Y3" s="14"/>
-      <c r="Z3" s="14"/>
-      <c r="AA3" s="15"/>
+        <v>12</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="N3" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="O3" s="16"/>
+      <c r="P3" s="16"/>
+      <c r="Q3" s="16"/>
+      <c r="R3" s="16"/>
+      <c r="S3" s="16"/>
+      <c r="T3" s="16"/>
+      <c r="U3" s="16"/>
+      <c r="V3" s="16"/>
+      <c r="W3" s="16"/>
+      <c r="X3" s="16"/>
+      <c r="Y3" s="16"/>
+      <c r="Z3" s="16"/>
+      <c r="AA3" s="17"/>
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="1">
         <v>10001</v>
       </c>
-      <c r="C4" s="7" t="s">
-        <v>25</v>
+      <c r="C4" s="8" t="s">
+        <v>15</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="H4" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="I4" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="J4" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="K4" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="L4" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="M4" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="N4" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="O4" s="5">
+        <v>17</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="I4" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="J4" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="K4" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="L4" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="M4" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="N4" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="O4" s="6">
         <v>0.5</v>
       </c>
     </row>
@@ -859,175 +871,175 @@
       <c r="B5" s="1">
         <v>10002</v>
       </c>
-      <c r="C5" s="7" t="s">
-        <v>31</v>
+      <c r="C5" s="8" t="s">
+        <v>21</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>27</v>
+        <v>22</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>17</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="H5" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="I5" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="J5" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="K5" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="L5" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="M5" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="N5" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="O5" s="6" t="s">
-        <v>34</v>
+        <v>17</v>
+      </c>
+      <c r="H5" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="I5" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="J5" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="K5" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="L5" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="M5" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="N5" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="O5" s="7" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="B6" s="4">
+      <c r="B6" s="5">
         <v>1003</v>
       </c>
-      <c r="C6" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="E6" s="6" t="s">
+      <c r="C6" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="H6" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="I6" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="J6" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="K6" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="L6" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="M6" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="N6" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="O6" s="5" t="s">
         <v>27</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="G6" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="H6" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="I6" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="J6" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="K6" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="L6" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="M6" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="N6" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="O6" s="4" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="B7" s="3">
+      <c r="B7" s="4">
         <v>1005</v>
       </c>
-      <c r="C7" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="G7" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="H7" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="I7" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="J7" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="K7" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="L7" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="M7" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="N7" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="O7" s="3" t="s">
-        <v>40</v>
+      <c r="C7" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="H7" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="I7" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="J7" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="K7" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="L7" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="M7" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="N7" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="O7" s="4" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="8" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="B8" s="2">
+      <c r="B8" s="3">
         <v>20001</v>
       </c>
-      <c r="C8" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="G8" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="H8" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="I8" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="J8" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="K8" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="L8" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="M8" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="N8" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="O8">
+      <c r="C8" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="H8" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="I8" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="J8" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="K8" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="L8" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="M8" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="N8" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="O8" s="2">
         <v>101</v>
       </c>
     </row>
